--- a/test/fixtures/xlsx/optional/optional.xlsx
+++ b/test/fixtures/xlsx/optional/optional.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="70">
   <si>
     <t xml:space="preserve">~~enum:Rarity~~</t>
   </si>
@@ -216,6 +216,9 @@
   </si>
   <si>
     <t xml:space="preserve">true</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-</t>
   </si>
   <si>
     <t xml:space="preserve">3</t>
@@ -572,78 +575,78 @@
         <v>57</v>
       </c>
       <c r="H10" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="I10" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="J10" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="K10" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="L10" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="M10" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="N10" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="O10" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="P10" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="Q10" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="R10" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11">
       <c r="F11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G11" t="s">
         <v>57</v>
       </c>
       <c r="H11" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="I11" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="J11" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="K11" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="L11" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="M11" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="N11" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="O11" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="P11" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="Q11" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
       <c r="R11" t="s">
-        <v>19</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/test/fixtures/xlsx/optional/optional.xlsx
+++ b/test/fixtures/xlsx/optional/optional.xlsx
@@ -12,21 +12,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="70">
-  <si>
-    <t xml:space="preserve">~~enum:Rarity~~</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="72">
+  <si>
+    <t xml:space="preserve">:enum Rarity</t>
   </si>
   <si>
     <t xml:space="preserve">Rarity of a drop.</t>
   </si>
   <si>
-    <t xml:space="preserve">name</t>
+    <t xml:space="preserve">:field</t>
+  </si>
+  <si>
+    <t xml:space="preserve">label</t>
   </si>
   <si>
     <t xml:space="preserve">value</t>
   </si>
   <si>
-    <t xml:space="preserve">description</t>
+    <t xml:space="preserve">desc</t>
   </si>
   <si>
     <t xml:space="preserve">None</t>
@@ -56,24 +59,30 @@
     <t xml:space="preserve">rare</t>
   </si>
   <si>
-    <t xml:space="preserve">~~table:Drop~~</t>
+    <t xml:space="preserve">:table Drop</t>
   </si>
   <si>
     <t xml:space="preserve">Optional columns, each beside the same type left required.</t>
   </si>
   <si>
+    <t xml:space="preserve">:type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">:desc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">:target</t>
+  </si>
+  <si>
     <t xml:space="preserve">index</t>
   </si>
   <si>
+    <t xml:space="preserve">int</t>
+  </si>
+  <si>
     <t xml:space="preserve">primary index, never optional</t>
   </si>
   <si>
-    <t xml:space="preserve">int</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
     <t xml:space="preserve">cs</t>
   </si>
   <si>
@@ -86,103 +95,100 @@
     <t xml:space="preserve">Bonus</t>
   </si>
   <si>
+    <t xml:space="preserve">int?</t>
+  </si>
+  <si>
     <t xml:space="preserve">optional int</t>
   </si>
   <si>
-    <t xml:space="preserve">int?</t>
-  </si>
-  <si>
     <t xml:space="preserve">Weight</t>
   </si>
   <si>
+    <t xml:space="preserve">double?</t>
+  </si>
+  <si>
     <t xml:space="preserve">optional double</t>
   </si>
   <si>
-    <t xml:space="preserve">double?</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ratio</t>
   </si>
   <si>
+    <t xml:space="preserve">float?</t>
+  </si>
+  <si>
     <t xml:space="preserve">optional float</t>
   </si>
   <si>
-    <t xml:space="preserve">float?</t>
-  </si>
-  <si>
     <t xml:space="preserve">Count</t>
   </si>
   <si>
+    <t xml:space="preserve">bigint?</t>
+  </si>
+  <si>
     <t xml:space="preserve">optional bigint</t>
   </si>
   <si>
-    <t xml:space="preserve">bigint?</t>
-  </si>
-  <si>
     <t xml:space="preserve">OpenAt</t>
   </si>
   <si>
+    <t xml:space="preserve">datetime?</t>
+  </si>
+  <si>
     <t xml:space="preserve">optional datetime</t>
   </si>
   <si>
-    <t xml:space="preserve">datetime?</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cooldown</t>
   </si>
   <si>
+    <t xml:space="preserve">timespan?</t>
+  </si>
+  <si>
     <t xml:space="preserve">optional timespan</t>
   </si>
   <si>
-    <t xml:space="preserve">timespan?</t>
-  </si>
-  <si>
     <t xml:space="preserve">Batch</t>
   </si>
   <si>
+    <t xml:space="preserve">uuid?</t>
+  </si>
+  <si>
     <t xml:space="preserve">optional uuid</t>
   </si>
   <si>
-    <t xml:space="preserve">uuid?</t>
-  </si>
-  <si>
     <t xml:space="preserve">Grade</t>
   </si>
   <si>
+    <t xml:space="preserve">Rarity?</t>
+  </si>
+  <si>
     <t xml:space="preserve">optional enum label</t>
   </si>
   <si>
-    <t xml:space="preserve">enum?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rarity</t>
-  </si>
-  <si>
     <t xml:space="preserve">Costs</t>
   </si>
   <si>
+    <t xml:space="preserve">int[]?</t>
+  </si>
+  <si>
     <t xml:space="preserve">optional array</t>
   </si>
   <si>
-    <t xml:space="preserve">int[]?</t>
-  </si>
-  <si>
     <t xml:space="preserve">Label</t>
   </si>
   <si>
+    <t xml:space="preserve">string?</t>
+  </si>
+  <si>
     <t xml:space="preserve">optional string</t>
   </si>
   <si>
-    <t xml:space="preserve">string?</t>
-  </si>
-  <si>
     <t xml:space="preserve">Hidden</t>
   </si>
   <si>
+    <t xml:space="preserve">bool?</t>
+  </si>
+  <si>
     <t xml:space="preserve">optional bool</t>
-  </si>
-  <si>
-    <t xml:space="preserve">bool?</t>
   </si>
   <si>
     <t xml:space="preserve">100</t>
@@ -266,64 +272,118 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="B2:R11"/>
+  <dimension ref="B2:S9"/>
   <sheetFormatPr defaultColWidth="8.43" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
       <c r="B2" t="s">
         <v>0</v>
       </c>
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="G2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" t="s">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" t="s">
+        <v>5</v>
       </c>
       <c r="F3" t="s">
-        <v>15</v>
+        <v>2</v>
+      </c>
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K3" t="s">
+        <v>32</v>
+      </c>
+      <c r="L3" t="s">
+        <v>35</v>
+      </c>
+      <c r="M3" t="s">
+        <v>38</v>
+      </c>
+      <c r="N3" t="s">
+        <v>41</v>
+      </c>
+      <c r="O3" t="s">
+        <v>44</v>
+      </c>
+      <c r="P3" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>50</v>
+      </c>
+      <c r="R3" t="s">
+        <v>53</v>
+      </c>
+      <c r="S3" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="4">
-      <c r="B4" t="s">
-        <v>2</v>
-      </c>
       <c r="C4" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D4" t="s">
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G4" t="s">
         <v>21</v>
       </c>
       <c r="H4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="I4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P4" t="s">
         <v>48</v>
@@ -334,46 +394,49 @@
       <c r="R4" t="s">
         <v>54</v>
       </c>
+      <c r="S4" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="5">
-      <c r="B5" t="s">
-        <v>5</v>
-      </c>
       <c r="C5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D5" t="s">
-        <v>7</v>
+        <v>10</v>
+      </c>
+      <c r="E5" t="s">
+        <v>11</v>
       </c>
       <c r="F5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G5" t="s">
         <v>22</v>
       </c>
       <c r="H5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="P5" t="s">
         <v>49</v>
@@ -384,269 +447,184 @@
       <c r="R5" t="s">
         <v>55</v>
       </c>
+      <c r="S5" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="6">
-      <c r="B6" t="s">
-        <v>8</v>
-      </c>
       <c r="C6" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L6" t="s">
+        <v>23</v>
+      </c>
+      <c r="M6" t="s">
+        <v>23</v>
+      </c>
+      <c r="N6" t="s">
+        <v>23</v>
+      </c>
+      <c r="O6" t="s">
+        <v>23</v>
+      </c>
+      <c r="P6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>23</v>
+      </c>
+      <c r="R6" t="s">
+        <v>23</v>
+      </c>
+      <c r="S6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="G7" t="s">
         <v>10</v>
       </c>
-      <c r="F6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I6" t="s">
-        <v>28</v>
-      </c>
-      <c r="J6" t="s">
-        <v>31</v>
-      </c>
-      <c r="K6" t="s">
-        <v>34</v>
-      </c>
-      <c r="L6" t="s">
-        <v>37</v>
-      </c>
-      <c r="M6" t="s">
-        <v>40</v>
-      </c>
-      <c r="N6" t="s">
-        <v>43</v>
-      </c>
-      <c r="O6" t="s">
-        <v>46</v>
-      </c>
-      <c r="P6" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>53</v>
-      </c>
-      <c r="R6" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="H7" t="s">
+        <v>59</v>
+      </c>
+      <c r="I7" t="s">
+        <v>60</v>
+      </c>
+      <c r="J7" t="s">
+        <v>61</v>
+      </c>
+      <c r="K7" t="s">
+        <v>62</v>
+      </c>
+      <c r="L7" t="s">
+        <v>63</v>
+      </c>
+      <c r="M7" t="s">
+        <v>64</v>
+      </c>
+      <c r="N7" t="s">
+        <v>65</v>
+      </c>
+      <c r="O7" t="s">
+        <v>66</v>
+      </c>
+      <c r="P7" t="s">
         <v>12</v>
       </c>
-      <c r="D7" t="s">
+      <c r="Q7" t="s">
+        <v>67</v>
+      </c>
+      <c r="R7" t="s">
+        <v>68</v>
+      </c>
+      <c r="S7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="G8" t="s">
         <v>13</v>
       </c>
-      <c r="F7" t="s">
-        <v>19</v>
-      </c>
-      <c r="G7" t="s">
-        <v>19</v>
-      </c>
-      <c r="H7" t="s">
-        <v>19</v>
-      </c>
-      <c r="I7" t="s">
-        <v>19</v>
-      </c>
-      <c r="J7" t="s">
-        <v>19</v>
-      </c>
-      <c r="K7" t="s">
-        <v>19</v>
-      </c>
-      <c r="L7" t="s">
-        <v>19</v>
-      </c>
-      <c r="M7" t="s">
-        <v>19</v>
-      </c>
-      <c r="N7" t="s">
-        <v>19</v>
-      </c>
-      <c r="O7" t="s">
-        <v>47</v>
-      </c>
-      <c r="P7" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>19</v>
-      </c>
-      <c r="R7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="F8" t="s">
-        <v>20</v>
-      </c>
-      <c r="G8" t="s">
-        <v>20</v>
-      </c>
       <c r="H8" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="I8" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="J8" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="K8" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="L8" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="M8" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="N8" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="O8" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="P8" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="Q8" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="R8" t="s">
-        <v>20</v>
+        <v>70</v>
+      </c>
+      <c r="S8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="9">
-      <c r="F9" t="s">
-        <v>9</v>
-      </c>
       <c r="G9" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="H9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I9" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="J9" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="K9" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="L9" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="M9" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="N9" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="O9" t="s">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="P9" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="Q9" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="R9" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="F10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10" t="s">
-        <v>57</v>
-      </c>
-      <c r="H10" t="s">
-        <v>68</v>
-      </c>
-      <c r="I10" t="s">
-        <v>68</v>
-      </c>
-      <c r="J10" t="s">
-        <v>68</v>
-      </c>
-      <c r="K10" t="s">
-        <v>68</v>
-      </c>
-      <c r="L10" t="s">
-        <v>68</v>
-      </c>
-      <c r="M10" t="s">
-        <v>68</v>
-      </c>
-      <c r="N10" t="s">
-        <v>68</v>
-      </c>
-      <c r="O10" t="s">
-        <v>68</v>
-      </c>
-      <c r="P10" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>68</v>
-      </c>
-      <c r="R10" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="F11" t="s">
-        <v>69</v>
-      </c>
-      <c r="G11" t="s">
-        <v>57</v>
-      </c>
-      <c r="H11" t="s">
-        <v>68</v>
-      </c>
-      <c r="I11" t="s">
-        <v>68</v>
-      </c>
-      <c r="J11" t="s">
-        <v>68</v>
-      </c>
-      <c r="K11" t="s">
-        <v>68</v>
-      </c>
-      <c r="L11" t="s">
-        <v>68</v>
-      </c>
-      <c r="M11" t="s">
-        <v>68</v>
-      </c>
-      <c r="N11" t="s">
-        <v>68</v>
-      </c>
-      <c r="O11" t="s">
-        <v>68</v>
-      </c>
-      <c r="P11" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>68</v>
-      </c>
-      <c r="R11" t="s">
-        <v>68</v>
+        <v>70</v>
+      </c>
+      <c r="S9" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
